--- a/evals/datasets/document_extraction/files/DOC-107.xlsx
+++ b/evals/datasets/document_extraction/files/DOC-107.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,7 +426,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Invoice INV-46586</t>
+          <t>Tax invoice</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>INV-46586</t>
         </is>
       </c>
     </row>
@@ -445,7 +450,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>Your order</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -457,42 +462,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Code or description</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Unit price</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Amount EUR</t>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Net</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>SYR-LL-5</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>6.10</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>305.00</t>
         </is>
@@ -501,20 +516,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Children's adhesive plasters with drawings</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>3.11</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>15.55</t>
         </is>
@@ -523,7 +543,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Handling charge: 24.41 EUR</t>
+          <t>Handling and packing</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>24.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Invoice total in EUR</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>344.96</t>
         </is>
       </c>
     </row>
